--- a/持仓跟踪.xlsx
+++ b/持仓跟踪.xlsx
@@ -168,54 +168,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing_wm1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6800000" y="6400000"/>
-    <xdr:ext cx="2200000" cy="350000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2200000" cy="350000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>TRAE AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -500,7 +452,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -682,6 +634,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>